--- a/planos_empresas/plano_empresa_00095.xlsx
+++ b/planos_empresas/plano_empresa_00095.xlsx
@@ -413,9 +413,310 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>010501 - Licenciamento ou cessão de direito de uso de programas de computação.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>3353</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>010601 - Assessoria e consultoria em informática.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>010701 - Suporte técnico em informática, inclusive instalação, configuração e manutenção de programas de computação e bancos de dados.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3066</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>042201 - Planos de medicina de grupo ou individual e convênios para prestação de assistência médica, hospitalar, odontológica e congêneres.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>070202 - Execução, por empreitada ou subempreitada, de obras de construção civil, hidráulica ou elétrica e de outras obras semelhantes, inclusive sondagem, perfuração de poços, escavação, drenagem e irrigação, terraplanagem, pavimentação, concretagem e a instalação e montagem de produtos, peças e equipamentos (exceto o fornecimento de mercadorias produzidas pelo prestador de serviços fora do local da prestação dos serviços, que fica sujeito ao ICMS).</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3066</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>070901 - Varrição, coleta e remoção de lixo, rejeitos e outros resíduos quaisquer.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3248</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>100501 - Agenciamento, corretagem ou intermediacao de bens moveis ou imoveis, nao abrangidos em outros itens ou subitens, por quaisquer meios.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>100901 - Representação de qualquer natureza, inclusive comercial.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>110401 - Armazenamento, depósito, guarda de bens de qualquer espécie.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3346</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>140101 - Lubrificação, limpeza, lustração, revisão, carga e recarga, conserto, restauração, blindagem, manutenção e conservação de máquinas, veículos, aparelhos, equipamentos, motores, elevadores ou de qualquer objeto (exceto peças e partes empregadas, que ficam sujeitas ao ICMS).</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3066</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>140201 - Assistência técnica.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>140701 - Colocação de molduras e congêneres.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>170101 - Assessoria ou consultoria de qualquer natureza, não contida em outros itens desta lista.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>170301 - Planejamento, coordenação, programação ou organização técnica.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>170303 - Planejamento, coordenação, programação ou organização administrativa.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>171201 - Administração em geral, inclusive de bens e negócios de terceiros.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>171401 - Advocacia</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>171901 - Contabilidade, inclusive serviços técnicos e auxiliares.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3339</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>260101 - Serviços de coleta, remessa ou entrega de correspondências, documentos, objetos, bens ou valores, inclusive pelos correios e suas agências franqueadas.</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3346</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>310104 - Serviços técnicos em telecomunicações e congêneres.</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>